--- a/artfynd/A 44736-2021 artfynd.xlsx
+++ b/artfynd/A 44736-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123594578</v>
       </c>
       <c r="B2" t="n">
-        <v>91019</v>
+        <v>91036</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 44736-2021 artfynd.xlsx
+++ b/artfynd/A 44736-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123594578</v>
       </c>
       <c r="B2" t="n">
-        <v>91036</v>
+        <v>91041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 44736-2021 artfynd.xlsx
+++ b/artfynd/A 44736-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123594578</v>
       </c>
       <c r="B2" t="n">
-        <v>91041</v>
+        <v>91043</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
